--- a/out/lunch_restaurants.xlsx
+++ b/out/lunch_restaurants.xlsx
@@ -18,6 +18,8 @@
     <sheet name="회·해산물" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="양식·아시안" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="롯데백화점" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="디저트" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="기타" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">전체!$A$9:$O$79</definedName>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="206">
   <si>
     <r>
       <rPr>
@@ -70,7 +72,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(36</t>
+      <t xml:space="preserve">(43</t>
     </r>
     <r>
       <rPr>
@@ -3296,6 +3298,791 @@
   </si>
   <si>
     <t xml:space="preserve">돼지고기와 묵은지 반반 김치찌개</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이재모피자 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광복동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광복동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상세 주소 확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상세는 이름만 받음 – 확인 필요</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">샤브남바완</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">샤브샤브 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이름만 받음 – 위치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업종 확인 필요 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분류 추정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">기타</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미쓰부산</t>
+  </si>
+  <si>
+    <t xml:space="preserve">확인 필요</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이름만 받음 – 업종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위치 확인 필요</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">디저트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미미당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빙수</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★4.81 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리뷰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,024)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국산팥 빙수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">네이버 쿠폰 있음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">더타임나우</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카페</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디저트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★4.82 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리뷰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,063)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">복숭아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">멜론 크로플 한정판매 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수제 디저트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">블렌딩티</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보노베리 광복점</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부산 중구 광복중앙로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">28-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리뷰 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">343</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">무화과 케이크</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라스트오더 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중앙역 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번 출구 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">532m / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리뷰 이벤트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026.09.28~10.15 (2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">천원 더블적립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">망고빙수 집 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이름 확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빙수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">망고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">망고빙수</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">링크 검색어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">남포동 케이크 맛집 – 가게 이름 확인 필요</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://map.naver.com/p/entry/place/1693420290</t>
   </si>
   <si>
     <r>
@@ -4026,7 +4813,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="28">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4061,6 +4848,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFDDEBF7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -4070,6 +4865,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE4D2B8"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -4209,6 +5012,20 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4D2B8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -4238,7 +5055,7 @@
       <rgbColor rgb="FFBDD7EE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
@@ -4248,14 +5065,14 @@
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFE699"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFF4B6C2"/>
       <rgbColor rgb="FFEAD1F5"/>
-      <rgbColor rgb="FFF4B6C2"/>
-      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFE4D2B8"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
@@ -4510,13 +5327,13 @@
       </c>
       <c r="C5" s="5" t="str">
         <f aca="false">IF($J$6="","후보 없음",INDEX($C$10:$C$79,$J$6))</f>
-        <v>수수하지만장해 롯데백화점 광복점</v>
+        <v>동해반점</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="str">
         <f aca="false">IF($J$6="","",INDEX($D$10:$D$79,$J$6)&amp;" · "&amp;INDEX($G$10:$G$79,$J$6)&amp;" "&amp;INDEX($H$10:$H$79,$J$6))</f>
-        <v>돈가스 · 부산 중구 중앙동7가 20-1 (롯데백화점 광복점) 본관 B1</v>
+        <v>중식당 · 부산 중구 중앙동6가 3-1 </v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4533,21 +5350,21 @@
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">IF($C$4="전체",COUNTA($C$10:$C$79),COUNTIF($B$10:$B$79,$C$4))</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="7" t="n">
         <f aca="false">IF($E$6=0,"",RANDBETWEEN(1,$E$6))</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">IF($E$6=0,"",IF($C$4="전체",$H$6,MATCH($C$4&amp;"|"&amp;$H$6,$P$10:$P$79,0)))</f>
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6076,16 +6893,26 @@
       <c r="Q45" s="20"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="str">
+      <c r="A46" s="11" t="n">
         <f aca="false">IF(C46="","",ROW()-9)</f>
-        <v/>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="F46" s="15"/>
-      <c r="G46" s="17"/>
+      <c r="G46" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="H46" s="17"/>
       <c r="I46" s="15"/>
       <c r="J46" s="17"/>
@@ -6096,22 +6923,32 @@
       </c>
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
-      <c r="O46" s="17"/>
+      <c r="O46" s="14" t="s">
+        <v>167</v>
+      </c>
       <c r="P46" s="19" t="str">
         <f aca="false">IF(OR(B46="",C46=""),"",B46&amp;"|"&amp;COUNTIF($B$10:B46,B46))</f>
-        <v/>
+        <v>양식·아시안|2</v>
       </c>
       <c r="Q46" s="20"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="str">
+    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11" t="n">
         <f aca="false">IF(C47="","",ROW()-9)</f>
-        <v/>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="F47" s="15"/>
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
@@ -6124,22 +6961,32 @@
       </c>
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
-      <c r="O47" s="17"/>
+      <c r="O47" s="14" t="s">
+        <v>170</v>
+      </c>
       <c r="P47" s="19" t="str">
         <f aca="false">IF(OR(B47="",C47=""),"",B47&amp;"|"&amp;COUNTIF($B$10:B47,B47))</f>
-        <v/>
+        <v>일식|4</v>
       </c>
       <c r="Q47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11" t="str">
+      <c r="A48" s="11" t="n">
         <f aca="false">IF(C48="","",ROW()-9)</f>
-        <v/>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="15"/>
+        <v>39</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="F48" s="15"/>
       <c r="G48" s="17"/>
       <c r="H48" s="17"/>
@@ -6152,124 +6999,188 @@
       </c>
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
-      <c r="O48" s="17"/>
+      <c r="O48" s="14" t="s">
+        <v>174</v>
+      </c>
       <c r="P48" s="19" t="str">
         <f aca="false">IF(OR(B48="",C48=""),"",B48&amp;"|"&amp;COUNTIF($B$10:B48,B48))</f>
-        <v/>
+        <v>기타|1</v>
       </c>
       <c r="Q48" s="20"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="str">
+    <row r="49" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="11" t="n">
         <f aca="false">IF(C49="","",ROW()-9)</f>
-        <v/>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="F49" s="15"/>
       <c r="G49" s="17"/>
       <c r="H49" s="17"/>
-      <c r="I49" s="15"/>
+      <c r="I49" s="22" t="s">
+        <v>178</v>
+      </c>
       <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
+      <c r="K49" s="16" t="s">
+        <v>179</v>
+      </c>
       <c r="L49" s="18" t="str">
         <f aca="false">IF(Q49="","",HYPERLINK(Q49,"지도"))</f>
         <v/>
       </c>
       <c r="M49" s="15"/>
       <c r="N49" s="15"/>
-      <c r="O49" s="17"/>
+      <c r="O49" s="14" t="s">
+        <v>180</v>
+      </c>
       <c r="P49" s="19" t="str">
         <f aca="false">IF(OR(B49="",C49=""),"",B49&amp;"|"&amp;COUNTIF($B$10:B49,B49))</f>
-        <v/>
+        <v>디저트|1</v>
       </c>
       <c r="Q49" s="20"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11" t="str">
+    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="11" t="n">
         <f aca="false">IF(C50="","",ROW()-9)</f>
-        <v/>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="15"/>
+        <v>41</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="F50" s="15"/>
       <c r="G50" s="17"/>
       <c r="H50" s="17"/>
-      <c r="I50" s="15"/>
+      <c r="I50" s="22" t="s">
+        <v>183</v>
+      </c>
       <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
+      <c r="K50" s="14" t="s">
+        <v>184</v>
+      </c>
       <c r="L50" s="18" t="str">
         <f aca="false">IF(Q50="","",HYPERLINK(Q50,"지도"))</f>
         <v/>
       </c>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
-      <c r="O50" s="17"/>
+      <c r="O50" s="14" t="s">
+        <v>180</v>
+      </c>
       <c r="P50" s="19" t="str">
         <f aca="false">IF(OR(B50="",C50=""),"",B50&amp;"|"&amp;COUNTIF($B$10:B50,B50))</f>
-        <v/>
+        <v>디저트|2</v>
       </c>
       <c r="Q50" s="20"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="str">
+    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="11" t="n">
         <f aca="false">IF(C51="","",ROW()-9)</f>
-        <v/>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="15"/>
+        <v>42</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>187</v>
+      </c>
       <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
+      <c r="K51" s="14" t="s">
+        <v>188</v>
+      </c>
       <c r="L51" s="18" t="str">
         <f aca="false">IF(Q51="","",HYPERLINK(Q51,"지도"))</f>
         <v/>
       </c>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
-      <c r="O51" s="17"/>
+      <c r="O51" s="16" t="s">
+        <v>189</v>
+      </c>
       <c r="P51" s="19" t="str">
         <f aca="false">IF(OR(B51="",C51=""),"",B51&amp;"|"&amp;COUNTIF($B$10:B51,B51))</f>
-        <v/>
+        <v>디저트|3</v>
       </c>
       <c r="Q51" s="20"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="str">
+    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="11" t="n">
         <f aca="false">IF(C52="","",ROW()-9)</f>
-        <v/>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="F52" s="15"/>
       <c r="G52" s="17"/>
       <c r="H52" s="17"/>
       <c r="I52" s="15"/>
       <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
+      <c r="K52" s="14" t="s">
+        <v>192</v>
+      </c>
       <c r="L52" s="18" t="str">
         <f aca="false">IF(Q52="","",HYPERLINK(Q52,"지도"))</f>
-        <v/>
+        <v>지도</v>
       </c>
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
-      <c r="O52" s="17"/>
+      <c r="O52" s="14" t="s">
+        <v>193</v>
+      </c>
       <c r="P52" s="19" t="str">
         <f aca="false">IF(OR(B52="",C52=""),"",B52&amp;"|"&amp;COUNTIF($B$10:B52,B52))</f>
-        <v/>
-      </c>
-      <c r="Q52" s="20"/>
+        <v>디저트|4</v>
+      </c>
+      <c r="Q52" s="20" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="str">
@@ -7034,41 +7945,47 @@
     <mergeCell ref="F5:K5"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:B79">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>$B10="한식"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>$B10="고기·족발"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>$B10="국밥·탕"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>$B10="면"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>$B10="중식"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>$B10="일식"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>$B10="회·해산물"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>$B10="양식·아시안"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>$B10="롯데백화점"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+      <formula>$B10="디저트"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+      <formula>$B10="기타"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4" type="list">
-      <formula1>"전체,한식,고기·족발,국밥·탕,면,중식,일식,회·해산물,양식·아시안,롯데백화점"</formula1>
+      <formula1>"전체,한식,고기·족발,국밥·탕,면,중식,일식,회·해산물,양식·아시안,롯데백화점,디저트,기타"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B10:B79" type="list">
-      <formula1>"한식,고기·족발,국밥·탕,면,중식,일식,회·해산물,양식·아시안,롯데백화점"</formula1>
+      <formula1>"한식,고기·족발,국밥·탕,면,중식,일식,회·해산물,양식·아시안,롯데백화점,디저트,기타"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E79" type="list">
@@ -7127,7 +8044,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
         <v>83</v>
@@ -7171,13 +8088,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7674,6 +8591,3306 @@
       <c r="O12" s="30" t="n">
         <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;8,전체!$P$10:$P$79,0),"")</f>
         <v>36</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="str">
+        <f aca="false">IF($O13="","",9)</f>
+        <v/>
+      </c>
+      <c r="B13" s="28" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$C$10:$C$79,$O13)="","",INDEX(전체!$C$10:$C$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="C13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$D$10:$D$79,$O13)="","",INDEX(전체!$D$10:$D$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="D13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$E$10:$E$79,$O13)="","",INDEX(전체!$E$10:$E$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="E13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$F$10:$F$79,$O13)="","",INDEX(전체!$F$10:$F$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="F13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$G$10:$G$79,$O13)="","",INDEX(전체!$G$10:$G$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="G13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$H$10:$H$79,$O13)="","",INDEX(전체!$H$10:$H$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="H13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$I$10:$I$79,$O13)="","",INDEX(전체!$I$10:$I$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$J$10:$J$79,$O13)="","",INDEX(전체!$J$10:$J$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$K$10:$K$79,$O13)="","",INDEX(전체!$K$10:$K$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="18" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$Q$10:$Q$79,$O13)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O13),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$M$10:$M$79,$O13)="","",INDEX(전체!$M$10:$M$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$N$10:$N$79,$O13)="","",INDEX(전체!$N$10:$N$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$O$10:$O$79,$O13)="","",INDEX(전체!$O$10:$O$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="O13" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;9,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="str">
+        <f aca="false">IF($O14="","",10)</f>
+        <v/>
+      </c>
+      <c r="B14" s="28" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$C$10:$C$79,$O14)="","",INDEX(전체!$C$10:$C$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="C14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$D$10:$D$79,$O14)="","",INDEX(전체!$D$10:$D$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="D14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$E$10:$E$79,$O14)="","",INDEX(전체!$E$10:$E$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="E14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$F$10:$F$79,$O14)="","",INDEX(전체!$F$10:$F$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="F14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$G$10:$G$79,$O14)="","",INDEX(전체!$G$10:$G$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="G14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$H$10:$H$79,$O14)="","",INDEX(전체!$H$10:$H$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="H14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$I$10:$I$79,$O14)="","",INDEX(전체!$I$10:$I$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$J$10:$J$79,$O14)="","",INDEX(전체!$J$10:$J$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$K$10:$K$79,$O14)="","",INDEX(전체!$K$10:$K$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="18" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$Q$10:$Q$79,$O14)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O14),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$M$10:$M$79,$O14)="","",INDEX(전체!$M$10:$M$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="M14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$N$10:$N$79,$O14)="","",INDEX(전체!$N$10:$N$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="N14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$O$10:$O$79,$O14)="","",INDEX(전체!$O$10:$O$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="O14" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;10,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="str">
+        <f aca="false">IF($O15="","",11)</f>
+        <v/>
+      </c>
+      <c r="B15" s="28" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$C$10:$C$79,$O15)="","",INDEX(전체!$C$10:$C$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="C15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$D$10:$D$79,$O15)="","",INDEX(전체!$D$10:$D$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="D15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$E$10:$E$79,$O15)="","",INDEX(전체!$E$10:$E$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="E15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$F$10:$F$79,$O15)="","",INDEX(전체!$F$10:$F$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$G$10:$G$79,$O15)="","",INDEX(전체!$G$10:$G$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="G15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$H$10:$H$79,$O15)="","",INDEX(전체!$H$10:$H$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="H15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$I$10:$I$79,$O15)="","",INDEX(전체!$I$10:$I$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="I15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$J$10:$J$79,$O15)="","",INDEX(전체!$J$10:$J$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$K$10:$K$79,$O15)="","",INDEX(전체!$K$10:$K$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="K15" s="18" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$Q$10:$Q$79,$O15)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O15),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$M$10:$M$79,$O15)="","",INDEX(전체!$M$10:$M$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="M15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$N$10:$N$79,$O15)="","",INDEX(전체!$N$10:$N$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="N15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$O$10:$O$79,$O15)="","",INDEX(전체!$O$10:$O$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="O15" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;11,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="str">
+        <f aca="false">IF($O16="","",12)</f>
+        <v/>
+      </c>
+      <c r="B16" s="28" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$C$10:$C$79,$O16)="","",INDEX(전체!$C$10:$C$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="C16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$D$10:$D$79,$O16)="","",INDEX(전체!$D$10:$D$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="D16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$E$10:$E$79,$O16)="","",INDEX(전체!$E$10:$E$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="E16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$F$10:$F$79,$O16)="","",INDEX(전체!$F$10:$F$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="F16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$G$10:$G$79,$O16)="","",INDEX(전체!$G$10:$G$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="G16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$H$10:$H$79,$O16)="","",INDEX(전체!$H$10:$H$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="H16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$I$10:$I$79,$O16)="","",INDEX(전체!$I$10:$I$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="I16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$J$10:$J$79,$O16)="","",INDEX(전체!$J$10:$J$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$K$10:$K$79,$O16)="","",INDEX(전체!$K$10:$K$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="K16" s="18" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$Q$10:$Q$79,$O16)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O16),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$M$10:$M$79,$O16)="","",INDEX(전체!$M$10:$M$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="M16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$N$10:$N$79,$O16)="","",INDEX(전체!$N$10:$N$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="N16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$O$10:$O$79,$O16)="","",INDEX(전체!$O$10:$O$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="O16" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;12,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="str">
+        <f aca="false">IF($O17="","",13)</f>
+        <v/>
+      </c>
+      <c r="B17" s="28" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$C$10:$C$79,$O17)="","",INDEX(전체!$C$10:$C$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="C17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$D$10:$D$79,$O17)="","",INDEX(전체!$D$10:$D$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="D17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$E$10:$E$79,$O17)="","",INDEX(전체!$E$10:$E$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="E17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$F$10:$F$79,$O17)="","",INDEX(전체!$F$10:$F$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="F17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$G$10:$G$79,$O17)="","",INDEX(전체!$G$10:$G$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="G17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$H$10:$H$79,$O17)="","",INDEX(전체!$H$10:$H$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="H17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$I$10:$I$79,$O17)="","",INDEX(전체!$I$10:$I$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="I17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$J$10:$J$79,$O17)="","",INDEX(전체!$J$10:$J$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$K$10:$K$79,$O17)="","",INDEX(전체!$K$10:$K$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="18" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$Q$10:$Q$79,$O17)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O17),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$M$10:$M$79,$O17)="","",INDEX(전체!$M$10:$M$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="M17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$N$10:$N$79,$O17)="","",INDEX(전체!$N$10:$N$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="N17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$O$10:$O$79,$O17)="","",INDEX(전체!$O$10:$O$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="O17" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;13,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="str">
+        <f aca="false">IF($O18="","",14)</f>
+        <v/>
+      </c>
+      <c r="B18" s="28" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$C$10:$C$79,$O18)="","",INDEX(전체!$C$10:$C$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="C18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$D$10:$D$79,$O18)="","",INDEX(전체!$D$10:$D$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="D18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$E$10:$E$79,$O18)="","",INDEX(전체!$E$10:$E$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="E18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$F$10:$F$79,$O18)="","",INDEX(전체!$F$10:$F$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="F18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$G$10:$G$79,$O18)="","",INDEX(전체!$G$10:$G$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="G18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$H$10:$H$79,$O18)="","",INDEX(전체!$H$10:$H$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="H18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$I$10:$I$79,$O18)="","",INDEX(전체!$I$10:$I$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="I18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$J$10:$J$79,$O18)="","",INDEX(전체!$J$10:$J$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$K$10:$K$79,$O18)="","",INDEX(전체!$K$10:$K$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="K18" s="18" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$Q$10:$Q$79,$O18)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O18),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$M$10:$M$79,$O18)="","",INDEX(전체!$M$10:$M$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="M18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$N$10:$N$79,$O18)="","",INDEX(전체!$N$10:$N$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="N18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$O$10:$O$79,$O18)="","",INDEX(전체!$O$10:$O$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="O18" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;14,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="str">
+        <f aca="false">IF($O19="","",15)</f>
+        <v/>
+      </c>
+      <c r="B19" s="28" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$C$10:$C$79,$O19)="","",INDEX(전체!$C$10:$C$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="C19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$D$10:$D$79,$O19)="","",INDEX(전체!$D$10:$D$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="D19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$E$10:$E$79,$O19)="","",INDEX(전체!$E$10:$E$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="E19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$F$10:$F$79,$O19)="","",INDEX(전체!$F$10:$F$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$G$10:$G$79,$O19)="","",INDEX(전체!$G$10:$G$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="G19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$H$10:$H$79,$O19)="","",INDEX(전체!$H$10:$H$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="H19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$I$10:$I$79,$O19)="","",INDEX(전체!$I$10:$I$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="I19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$J$10:$J$79,$O19)="","",INDEX(전체!$J$10:$J$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$K$10:$K$79,$O19)="","",INDEX(전체!$K$10:$K$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="K19" s="18" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$Q$10:$Q$79,$O19)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O19),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$M$10:$M$79,$O19)="","",INDEX(전체!$M$10:$M$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="M19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$N$10:$N$79,$O19)="","",INDEX(전체!$N$10:$N$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$O$10:$O$79,$O19)="","",INDEX(전체!$O$10:$O$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="O19" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;15,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="str">
+        <f aca="false">IF($O20="","",16)</f>
+        <v/>
+      </c>
+      <c r="B20" s="28" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$C$10:$C$79,$O20)="","",INDEX(전체!$C$10:$C$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="C20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$D$10:$D$79,$O20)="","",INDEX(전체!$D$10:$D$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="D20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$E$10:$E$79,$O20)="","",INDEX(전체!$E$10:$E$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="E20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$F$10:$F$79,$O20)="","",INDEX(전체!$F$10:$F$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="F20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$G$10:$G$79,$O20)="","",INDEX(전체!$G$10:$G$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="G20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$H$10:$H$79,$O20)="","",INDEX(전체!$H$10:$H$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="H20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$I$10:$I$79,$O20)="","",INDEX(전체!$I$10:$I$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="I20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$J$10:$J$79,$O20)="","",INDEX(전체!$J$10:$J$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$K$10:$K$79,$O20)="","",INDEX(전체!$K$10:$K$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="18" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$Q$10:$Q$79,$O20)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O20),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$M$10:$M$79,$O20)="","",INDEX(전체!$M$10:$M$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="M20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$N$10:$N$79,$O20)="","",INDEX(전체!$N$10:$N$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="N20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$O$10:$O$79,$O20)="","",INDEX(전체!$O$10:$O$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="O20" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;16,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="str">
+        <f aca="false">IF($O21="","",17)</f>
+        <v/>
+      </c>
+      <c r="B21" s="28" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$C$10:$C$79,$O21)="","",INDEX(전체!$C$10:$C$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="C21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$D$10:$D$79,$O21)="","",INDEX(전체!$D$10:$D$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="D21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$E$10:$E$79,$O21)="","",INDEX(전체!$E$10:$E$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="E21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$F$10:$F$79,$O21)="","",INDEX(전체!$F$10:$F$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="F21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$G$10:$G$79,$O21)="","",INDEX(전체!$G$10:$G$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$H$10:$H$79,$O21)="","",INDEX(전체!$H$10:$H$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="H21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$I$10:$I$79,$O21)="","",INDEX(전체!$I$10:$I$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="I21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$J$10:$J$79,$O21)="","",INDEX(전체!$J$10:$J$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$K$10:$K$79,$O21)="","",INDEX(전체!$K$10:$K$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="K21" s="18" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$Q$10:$Q$79,$O21)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O21),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$M$10:$M$79,$O21)="","",INDEX(전체!$M$10:$M$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="M21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$N$10:$N$79,$O21)="","",INDEX(전체!$N$10:$N$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="N21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$O$10:$O$79,$O21)="","",INDEX(전체!$O$10:$O$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="O21" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;17,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="str">
+        <f aca="false">IF($O22="","",18)</f>
+        <v/>
+      </c>
+      <c r="B22" s="28" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$C$10:$C$79,$O22)="","",INDEX(전체!$C$10:$C$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="C22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$D$10:$D$79,$O22)="","",INDEX(전체!$D$10:$D$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="D22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$E$10:$E$79,$O22)="","",INDEX(전체!$E$10:$E$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="E22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$F$10:$F$79,$O22)="","",INDEX(전체!$F$10:$F$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$G$10:$G$79,$O22)="","",INDEX(전체!$G$10:$G$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$H$10:$H$79,$O22)="","",INDEX(전체!$H$10:$H$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$I$10:$I$79,$O22)="","",INDEX(전체!$I$10:$I$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$J$10:$J$79,$O22)="","",INDEX(전체!$J$10:$J$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$K$10:$K$79,$O22)="","",INDEX(전체!$K$10:$K$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="K22" s="18" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$Q$10:$Q$79,$O22)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O22),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$M$10:$M$79,$O22)="","",INDEX(전체!$M$10:$M$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$N$10:$N$79,$O22)="","",INDEX(전체!$N$10:$N$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="N22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$O$10:$O$79,$O22)="","",INDEX(전체!$O$10:$O$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="O22" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;18,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="str">
+        <f aca="false">IF($O23="","",19)</f>
+        <v/>
+      </c>
+      <c r="B23" s="28" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$C$10:$C$79,$O23)="","",INDEX(전체!$C$10:$C$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="C23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$D$10:$D$79,$O23)="","",INDEX(전체!$D$10:$D$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="D23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$E$10:$E$79,$O23)="","",INDEX(전체!$E$10:$E$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="E23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$F$10:$F$79,$O23)="","",INDEX(전체!$F$10:$F$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="F23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$G$10:$G$79,$O23)="","",INDEX(전체!$G$10:$G$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$H$10:$H$79,$O23)="","",INDEX(전체!$H$10:$H$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="H23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$I$10:$I$79,$O23)="","",INDEX(전체!$I$10:$I$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$J$10:$J$79,$O23)="","",INDEX(전체!$J$10:$J$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$K$10:$K$79,$O23)="","",INDEX(전체!$K$10:$K$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="K23" s="18" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$Q$10:$Q$79,$O23)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O23),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$M$10:$M$79,$O23)="","",INDEX(전체!$M$10:$M$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="M23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$N$10:$N$79,$O23)="","",INDEX(전체!$N$10:$N$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="N23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$O$10:$O$79,$O23)="","",INDEX(전체!$O$10:$O$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="O23" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;19,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="str">
+        <f aca="false">IF($O24="","",20)</f>
+        <v/>
+      </c>
+      <c r="B24" s="28" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$C$10:$C$79,$O24)="","",INDEX(전체!$C$10:$C$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="C24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$D$10:$D$79,$O24)="","",INDEX(전체!$D$10:$D$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="D24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$E$10:$E$79,$O24)="","",INDEX(전체!$E$10:$E$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="E24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$F$10:$F$79,$O24)="","",INDEX(전체!$F$10:$F$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="F24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$G$10:$G$79,$O24)="","",INDEX(전체!$G$10:$G$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$H$10:$H$79,$O24)="","",INDEX(전체!$H$10:$H$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$I$10:$I$79,$O24)="","",INDEX(전체!$I$10:$I$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="I24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$J$10:$J$79,$O24)="","",INDEX(전체!$J$10:$J$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$K$10:$K$79,$O24)="","",INDEX(전체!$K$10:$K$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="K24" s="18" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$Q$10:$Q$79,$O24)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O24),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$M$10:$M$79,$O24)="","",INDEX(전체!$M$10:$M$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="M24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$N$10:$N$79,$O24)="","",INDEX(전체!$N$10:$N$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="N24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$O$10:$O$79,$O24)="","",INDEX(전체!$O$10:$O$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="O24" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;20,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="str">
+        <f aca="false">IF($O25="","",21)</f>
+        <v/>
+      </c>
+      <c r="B25" s="28" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$C$10:$C$79,$O25)="","",INDEX(전체!$C$10:$C$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="C25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$D$10:$D$79,$O25)="","",INDEX(전체!$D$10:$D$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="D25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$E$10:$E$79,$O25)="","",INDEX(전체!$E$10:$E$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="E25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$F$10:$F$79,$O25)="","",INDEX(전체!$F$10:$F$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="F25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$G$10:$G$79,$O25)="","",INDEX(전체!$G$10:$G$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$H$10:$H$79,$O25)="","",INDEX(전체!$H$10:$H$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$I$10:$I$79,$O25)="","",INDEX(전체!$I$10:$I$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$J$10:$J$79,$O25)="","",INDEX(전체!$J$10:$J$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$K$10:$K$79,$O25)="","",INDEX(전체!$K$10:$K$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="K25" s="18" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$Q$10:$Q$79,$O25)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O25),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$M$10:$M$79,$O25)="","",INDEX(전체!$M$10:$M$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="M25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$N$10:$N$79,$O25)="","",INDEX(전체!$N$10:$N$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="N25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$O$10:$O$79,$O25)="","",INDEX(전체!$O$10:$O$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="O25" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;21,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="str">
+        <f aca="false">IF($O26="","",22)</f>
+        <v/>
+      </c>
+      <c r="B26" s="28" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$C$10:$C$79,$O26)="","",INDEX(전체!$C$10:$C$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="C26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$D$10:$D$79,$O26)="","",INDEX(전체!$D$10:$D$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="D26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$E$10:$E$79,$O26)="","",INDEX(전체!$E$10:$E$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$F$10:$F$79,$O26)="","",INDEX(전체!$F$10:$F$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$G$10:$G$79,$O26)="","",INDEX(전체!$G$10:$G$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$H$10:$H$79,$O26)="","",INDEX(전체!$H$10:$H$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$I$10:$I$79,$O26)="","",INDEX(전체!$I$10:$I$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$J$10:$J$79,$O26)="","",INDEX(전체!$J$10:$J$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$K$10:$K$79,$O26)="","",INDEX(전체!$K$10:$K$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="K26" s="18" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$Q$10:$Q$79,$O26)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O26),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$M$10:$M$79,$O26)="","",INDEX(전체!$M$10:$M$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="M26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$N$10:$N$79,$O26)="","",INDEX(전체!$N$10:$N$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$O$10:$O$79,$O26)="","",INDEX(전체!$O$10:$O$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="O26" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;22,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="str">
+        <f aca="false">IF($O27="","",23)</f>
+        <v/>
+      </c>
+      <c r="B27" s="28" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$C$10:$C$79,$O27)="","",INDEX(전체!$C$10:$C$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="C27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$D$10:$D$79,$O27)="","",INDEX(전체!$D$10:$D$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="D27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$E$10:$E$79,$O27)="","",INDEX(전체!$E$10:$E$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="E27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$F$10:$F$79,$O27)="","",INDEX(전체!$F$10:$F$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="F27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$G$10:$G$79,$O27)="","",INDEX(전체!$G$10:$G$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$H$10:$H$79,$O27)="","",INDEX(전체!$H$10:$H$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$I$10:$I$79,$O27)="","",INDEX(전체!$I$10:$I$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="I27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$J$10:$J$79,$O27)="","",INDEX(전체!$J$10:$J$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$K$10:$K$79,$O27)="","",INDEX(전체!$K$10:$K$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="K27" s="18" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$Q$10:$Q$79,$O27)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O27),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$M$10:$M$79,$O27)="","",INDEX(전체!$M$10:$M$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="M27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$N$10:$N$79,$O27)="","",INDEX(전체!$N$10:$N$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="N27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$O$10:$O$79,$O27)="","",INDEX(전체!$O$10:$O$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="O27" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;23,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="str">
+        <f aca="false">IF($O28="","",24)</f>
+        <v/>
+      </c>
+      <c r="B28" s="28" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$C$10:$C$79,$O28)="","",INDEX(전체!$C$10:$C$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="C28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$D$10:$D$79,$O28)="","",INDEX(전체!$D$10:$D$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="D28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$E$10:$E$79,$O28)="","",INDEX(전체!$E$10:$E$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="E28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$F$10:$F$79,$O28)="","",INDEX(전체!$F$10:$F$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$G$10:$G$79,$O28)="","",INDEX(전체!$G$10:$G$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$H$10:$H$79,$O28)="","",INDEX(전체!$H$10:$H$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$I$10:$I$79,$O28)="","",INDEX(전체!$I$10:$I$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$J$10:$J$79,$O28)="","",INDEX(전체!$J$10:$J$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$K$10:$K$79,$O28)="","",INDEX(전체!$K$10:$K$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="K28" s="18" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$Q$10:$Q$79,$O28)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O28),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$M$10:$M$79,$O28)="","",INDEX(전체!$M$10:$M$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="M28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$N$10:$N$79,$O28)="","",INDEX(전체!$N$10:$N$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="N28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$O$10:$O$79,$O28)="","",INDEX(전체!$O$10:$O$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="O28" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;24,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="str">
+        <f aca="false">IF($O29="","",25)</f>
+        <v/>
+      </c>
+      <c r="B29" s="28" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$C$10:$C$79,$O29)="","",INDEX(전체!$C$10:$C$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="C29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$D$10:$D$79,$O29)="","",INDEX(전체!$D$10:$D$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="D29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$E$10:$E$79,$O29)="","",INDEX(전체!$E$10:$E$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="E29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$F$10:$F$79,$O29)="","",INDEX(전체!$F$10:$F$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="F29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$G$10:$G$79,$O29)="","",INDEX(전체!$G$10:$G$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="G29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$H$10:$H$79,$O29)="","",INDEX(전체!$H$10:$H$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$I$10:$I$79,$O29)="","",INDEX(전체!$I$10:$I$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="I29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$J$10:$J$79,$O29)="","",INDEX(전체!$J$10:$J$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$K$10:$K$79,$O29)="","",INDEX(전체!$K$10:$K$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="K29" s="18" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$Q$10:$Q$79,$O29)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O29),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$M$10:$M$79,$O29)="","",INDEX(전체!$M$10:$M$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="M29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$N$10:$N$79,$O29)="","",INDEX(전체!$N$10:$N$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="N29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$O$10:$O$79,$O29)="","",INDEX(전체!$O$10:$O$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="O29" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;25,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFE4D2B8"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" s="24" t="str">
+        <f aca="false">COUNTIF(전체!$B$10:$B$79,"디저트")&amp;"곳"</f>
+        <v>4곳</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q2" s="26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="n">
+        <f aca="false">IF($O5="","",1)</f>
+        <v>1</v>
+      </c>
+      <c r="B5" s="28" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$C$10:$C$79,$O5)="","",INDEX(전체!$C$10:$C$79,$O5)))</f>
+        <v>미미당</v>
+      </c>
+      <c r="C5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$D$10:$D$79,$O5)="","",INDEX(전체!$D$10:$D$79,$O5)))</f>
+        <v>빙수</v>
+      </c>
+      <c r="D5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$E$10:$E$79,$O5)="","",INDEX(전체!$E$10:$E$79,$O5)))</f>
+        <v>영업 중</v>
+      </c>
+      <c r="E5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$F$10:$F$79,$O5)="","",INDEX(전체!$F$10:$F$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="F5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$G$10:$G$79,$O5)="","",INDEX(전체!$G$10:$G$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="G5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$H$10:$H$79,$O5)="","",INDEX(전체!$H$10:$H$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="H5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$I$10:$I$79,$O5)="","",INDEX(전체!$I$10:$I$79,$O5)))</f>
+        <v>★4.81 (리뷰 1,024)</v>
+      </c>
+      <c r="I5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$J$10:$J$79,$O5)="","",INDEX(전체!$J$10:$J$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="J5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$K$10:$K$79,$O5)="","",INDEX(전체!$K$10:$K$79,$O5)))</f>
+        <v>100% 국산팥 빙수</v>
+      </c>
+      <c r="K5" s="18" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$Q$10:$Q$79,$O5)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O5),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$M$10:$M$79,$O5)="","",INDEX(전체!$M$10:$M$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="M5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$N$10:$N$79,$O5)="","",INDEX(전체!$N$10:$N$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="N5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$O$10:$O$79,$O5)="","",INDEX(전체!$O$10:$O$79,$O5)))</f>
+        <v>네이버 쿠폰 있음</v>
+      </c>
+      <c r="O5" s="30" t="n">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;1,전체!$P$10:$P$79,0),"")</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
+        <f aca="false">IF($O6="","",2)</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="28" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$C$10:$C$79,$O6)="","",INDEX(전체!$C$10:$C$79,$O6)))</f>
+        <v>더타임나우</v>
+      </c>
+      <c r="C6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$D$10:$D$79,$O6)="","",INDEX(전체!$D$10:$D$79,$O6)))</f>
+        <v>카페,디저트</v>
+      </c>
+      <c r="D6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$E$10:$E$79,$O6)="","",INDEX(전체!$E$10:$E$79,$O6)))</f>
+        <v>영업 중</v>
+      </c>
+      <c r="E6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$F$10:$F$79,$O6)="","",INDEX(전체!$F$10:$F$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="F6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$G$10:$G$79,$O6)="","",INDEX(전체!$G$10:$G$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="G6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$H$10:$H$79,$O6)="","",INDEX(전체!$H$10:$H$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="H6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$I$10:$I$79,$O6)="","",INDEX(전체!$I$10:$I$79,$O6)))</f>
+        <v>★4.82 (리뷰 2,063)</v>
+      </c>
+      <c r="I6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$J$10:$J$79,$O6)="","",INDEX(전체!$J$10:$J$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="J6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$K$10:$K$79,$O6)="","",INDEX(전체!$K$10:$K$79,$O6)))</f>
+        <v>복숭아&amp;멜론 크로플 한정판매 / 수제 디저트·블렌딩티</v>
+      </c>
+      <c r="K6" s="18" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$Q$10:$Q$79,$O6)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O6),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$M$10:$M$79,$O6)="","",INDEX(전체!$M$10:$M$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$N$10:$N$79,$O6)="","",INDEX(전체!$N$10:$N$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="N6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$O$10:$O$79,$O6)="","",INDEX(전체!$O$10:$O$79,$O6)))</f>
+        <v>네이버 쿠폰 있음</v>
+      </c>
+      <c r="O6" s="30" t="n">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;2,전체!$P$10:$P$79,0),"")</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="n">
+        <f aca="false">IF($O7="","",3)</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$C$10:$C$79,$O7)="","",INDEX(전체!$C$10:$C$79,$O7)))</f>
+        <v>보노베리 광복점</v>
+      </c>
+      <c r="C7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$D$10:$D$79,$O7)="","",INDEX(전체!$D$10:$D$79,$O7)))</f>
+        <v>카페,디저트</v>
+      </c>
+      <c r="D7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$E$10:$E$79,$O7)="","",INDEX(전체!$E$10:$E$79,$O7)))</f>
+        <v>영업 중</v>
+      </c>
+      <c r="E7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$F$10:$F$79,$O7)="","",INDEX(전체!$F$10:$F$79,$O7)))</f>
+        <v>O</v>
+      </c>
+      <c r="F7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$G$10:$G$79,$O7)="","",INDEX(전체!$G$10:$G$79,$O7)))</f>
+        <v>부산 중구 광복중앙로 28-1</v>
+      </c>
+      <c r="G7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$H$10:$H$79,$O7)="","",INDEX(전체!$H$10:$H$79,$O7)))</f>
+        <v>1,2층</v>
+      </c>
+      <c r="H7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$I$10:$I$79,$O7)="","",INDEX(전체!$I$10:$I$79,$O7)))</f>
+        <v>리뷰 343</v>
+      </c>
+      <c r="I7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$J$10:$J$79,$O7)="","",INDEX(전체!$J$10:$J$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$K$10:$K$79,$O7)="","",INDEX(전체!$K$10:$K$79,$O7)))</f>
+        <v>무화과 케이크</v>
+      </c>
+      <c r="K7" s="18" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$Q$10:$Q$79,$O7)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O7),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$M$10:$M$79,$O7)="","",INDEX(전체!$M$10:$M$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$N$10:$N$79,$O7)="","",INDEX(전체!$N$10:$N$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="N7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$O$10:$O$79,$O7)="","",INDEX(전체!$O$10:$O$79,$O7)))</f>
+        <v>20:30 라스트오더 / 중앙역 5번 출구 532m / 예약+리뷰 이벤트 2026.09.28~10.15 (2천원 더블적립)</v>
+      </c>
+      <c r="O7" s="30" t="n">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;3,전체!$P$10:$P$79,0),"")</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
+        <f aca="false">IF($O8="","",4)</f>
+        <v>4</v>
+      </c>
+      <c r="B8" s="28" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$C$10:$C$79,$O8)="","",INDEX(전체!$C$10:$C$79,$O8)))</f>
+        <v>망고빙수 집 (이름 확인 필요)</v>
+      </c>
+      <c r="C8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$D$10:$D$79,$O8)="","",INDEX(전체!$D$10:$D$79,$O8)))</f>
+        <v>빙수 (망고)</v>
+      </c>
+      <c r="D8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$E$10:$E$79,$O8)="","",INDEX(전체!$E$10:$E$79,$O8)))</f>
+        <v>정보 없음</v>
+      </c>
+      <c r="E8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$F$10:$F$79,$O8)="","",INDEX(전체!$F$10:$F$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="F8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$G$10:$G$79,$O8)="","",INDEX(전체!$G$10:$G$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$H$10:$H$79,$O8)="","",INDEX(전체!$H$10:$H$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="H8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$I$10:$I$79,$O8)="","",INDEX(전체!$I$10:$I$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$J$10:$J$79,$O8)="","",INDEX(전체!$J$10:$J$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$K$10:$K$79,$O8)="","",INDEX(전체!$K$10:$K$79,$O8)))</f>
+        <v>망고빙수</v>
+      </c>
+      <c r="K8" s="18" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$Q$10:$Q$79,$O8)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O8),"지도")))</f>
+        <v>지도</v>
+      </c>
+      <c r="L8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$M$10:$M$79,$O8)="","",INDEX(전체!$M$10:$M$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$N$10:$N$79,$O8)="","",INDEX(전체!$N$10:$N$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="N8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$O$10:$O$79,$O8)="","",INDEX(전체!$O$10:$O$79,$O8)))</f>
+        <v>링크 검색어: 남포동 케이크 맛집 – 가게 이름 확인 필요</v>
+      </c>
+      <c r="O8" s="30" t="n">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;4,전체!$P$10:$P$79,0),"")</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="str">
+        <f aca="false">IF($O9="","",5)</f>
+        <v/>
+      </c>
+      <c r="B9" s="28" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$C$10:$C$79,$O9)="","",INDEX(전체!$C$10:$C$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="C9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$D$10:$D$79,$O9)="","",INDEX(전체!$D$10:$D$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="D9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$E$10:$E$79,$O9)="","",INDEX(전체!$E$10:$E$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="E9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$F$10:$F$79,$O9)="","",INDEX(전체!$F$10:$F$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="F9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$G$10:$G$79,$O9)="","",INDEX(전체!$G$10:$G$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="G9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$H$10:$H$79,$O9)="","",INDEX(전체!$H$10:$H$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="H9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$I$10:$I$79,$O9)="","",INDEX(전체!$I$10:$I$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$J$10:$J$79,$O9)="","",INDEX(전체!$J$10:$J$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$K$10:$K$79,$O9)="","",INDEX(전체!$K$10:$K$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="18" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$Q$10:$Q$79,$O9)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O9),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$M$10:$M$79,$O9)="","",INDEX(전체!$M$10:$M$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$N$10:$N$79,$O9)="","",INDEX(전체!$N$10:$N$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="N9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$O$10:$O$79,$O9)="","",INDEX(전체!$O$10:$O$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="O9" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;5,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="str">
+        <f aca="false">IF($O10="","",6)</f>
+        <v/>
+      </c>
+      <c r="B10" s="28" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$C$10:$C$79,$O10)="","",INDEX(전체!$C$10:$C$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="C10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$D$10:$D$79,$O10)="","",INDEX(전체!$D$10:$D$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="D10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$E$10:$E$79,$O10)="","",INDEX(전체!$E$10:$E$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="E10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$F$10:$F$79,$O10)="","",INDEX(전체!$F$10:$F$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="F10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$G$10:$G$79,$O10)="","",INDEX(전체!$G$10:$G$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="G10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$H$10:$H$79,$O10)="","",INDEX(전체!$H$10:$H$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$I$10:$I$79,$O10)="","",INDEX(전체!$I$10:$I$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$J$10:$J$79,$O10)="","",INDEX(전체!$J$10:$J$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$K$10:$K$79,$O10)="","",INDEX(전체!$K$10:$K$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="18" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$Q$10:$Q$79,$O10)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O10),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$M$10:$M$79,$O10)="","",INDEX(전체!$M$10:$M$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$N$10:$N$79,$O10)="","",INDEX(전체!$N$10:$N$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="N10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$O$10:$O$79,$O10)="","",INDEX(전체!$O$10:$O$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="O10" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;6,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="str">
+        <f aca="false">IF($O11="","",7)</f>
+        <v/>
+      </c>
+      <c r="B11" s="28" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$C$10:$C$79,$O11)="","",INDEX(전체!$C$10:$C$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="C11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$D$10:$D$79,$O11)="","",INDEX(전체!$D$10:$D$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="D11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$E$10:$E$79,$O11)="","",INDEX(전체!$E$10:$E$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="E11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$F$10:$F$79,$O11)="","",INDEX(전체!$F$10:$F$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="F11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$G$10:$G$79,$O11)="","",INDEX(전체!$G$10:$G$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="G11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$H$10:$H$79,$O11)="","",INDEX(전체!$H$10:$H$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="H11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$I$10:$I$79,$O11)="","",INDEX(전체!$I$10:$I$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$J$10:$J$79,$O11)="","",INDEX(전체!$J$10:$J$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$K$10:$K$79,$O11)="","",INDEX(전체!$K$10:$K$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="18" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$Q$10:$Q$79,$O11)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O11),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$M$10:$M$79,$O11)="","",INDEX(전체!$M$10:$M$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$N$10:$N$79,$O11)="","",INDEX(전체!$N$10:$N$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="N11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$O$10:$O$79,$O11)="","",INDEX(전체!$O$10:$O$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="O11" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;7,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="str">
+        <f aca="false">IF($O12="","",8)</f>
+        <v/>
+      </c>
+      <c r="B12" s="28" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$C$10:$C$79,$O12)="","",INDEX(전체!$C$10:$C$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="C12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$D$10:$D$79,$O12)="","",INDEX(전체!$D$10:$D$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="D12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$E$10:$E$79,$O12)="","",INDEX(전체!$E$10:$E$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="E12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$F$10:$F$79,$O12)="","",INDEX(전체!$F$10:$F$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="F12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$G$10:$G$79,$O12)="","",INDEX(전체!$G$10:$G$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="G12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$H$10:$H$79,$O12)="","",INDEX(전체!$H$10:$H$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="H12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$I$10:$I$79,$O12)="","",INDEX(전체!$I$10:$I$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$J$10:$J$79,$O12)="","",INDEX(전체!$J$10:$J$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$K$10:$K$79,$O12)="","",INDEX(전체!$K$10:$K$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="18" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$Q$10:$Q$79,$O12)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O12),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$M$10:$M$79,$O12)="","",INDEX(전체!$M$10:$M$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$N$10:$N$79,$O12)="","",INDEX(전체!$N$10:$N$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$O$10:$O$79,$O12)="","",INDEX(전체!$O$10:$O$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="O12" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;8,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="str">
+        <f aca="false">IF($O13="","",9)</f>
+        <v/>
+      </c>
+      <c r="B13" s="28" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$C$10:$C$79,$O13)="","",INDEX(전체!$C$10:$C$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="C13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$D$10:$D$79,$O13)="","",INDEX(전체!$D$10:$D$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="D13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$E$10:$E$79,$O13)="","",INDEX(전체!$E$10:$E$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="E13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$F$10:$F$79,$O13)="","",INDEX(전체!$F$10:$F$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="F13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$G$10:$G$79,$O13)="","",INDEX(전체!$G$10:$G$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="G13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$H$10:$H$79,$O13)="","",INDEX(전체!$H$10:$H$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="H13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$I$10:$I$79,$O13)="","",INDEX(전체!$I$10:$I$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$J$10:$J$79,$O13)="","",INDEX(전체!$J$10:$J$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$K$10:$K$79,$O13)="","",INDEX(전체!$K$10:$K$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="18" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$Q$10:$Q$79,$O13)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O13),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$M$10:$M$79,$O13)="","",INDEX(전체!$M$10:$M$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="11" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$N$10:$N$79,$O13)="","",INDEX(전체!$N$10:$N$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="29" t="str">
+        <f aca="false">IF($O13="","",IF(INDEX(전체!$O$10:$O$79,$O13)="","",INDEX(전체!$O$10:$O$79,$O13)))</f>
+        <v/>
+      </c>
+      <c r="O13" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;9,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="str">
+        <f aca="false">IF($O14="","",10)</f>
+        <v/>
+      </c>
+      <c r="B14" s="28" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$C$10:$C$79,$O14)="","",INDEX(전체!$C$10:$C$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="C14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$D$10:$D$79,$O14)="","",INDEX(전체!$D$10:$D$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="D14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$E$10:$E$79,$O14)="","",INDEX(전체!$E$10:$E$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="E14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$F$10:$F$79,$O14)="","",INDEX(전체!$F$10:$F$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="F14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$G$10:$G$79,$O14)="","",INDEX(전체!$G$10:$G$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="G14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$H$10:$H$79,$O14)="","",INDEX(전체!$H$10:$H$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="H14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$I$10:$I$79,$O14)="","",INDEX(전체!$I$10:$I$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$J$10:$J$79,$O14)="","",INDEX(전체!$J$10:$J$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$K$10:$K$79,$O14)="","",INDEX(전체!$K$10:$K$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="18" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$Q$10:$Q$79,$O14)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O14),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$M$10:$M$79,$O14)="","",INDEX(전체!$M$10:$M$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="M14" s="11" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$N$10:$N$79,$O14)="","",INDEX(전체!$N$10:$N$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="N14" s="29" t="str">
+        <f aca="false">IF($O14="","",IF(INDEX(전체!$O$10:$O$79,$O14)="","",INDEX(전체!$O$10:$O$79,$O14)))</f>
+        <v/>
+      </c>
+      <c r="O14" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;10,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="str">
+        <f aca="false">IF($O15="","",11)</f>
+        <v/>
+      </c>
+      <c r="B15" s="28" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$C$10:$C$79,$O15)="","",INDEX(전체!$C$10:$C$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="C15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$D$10:$D$79,$O15)="","",INDEX(전체!$D$10:$D$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="D15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$E$10:$E$79,$O15)="","",INDEX(전체!$E$10:$E$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="E15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$F$10:$F$79,$O15)="","",INDEX(전체!$F$10:$F$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$G$10:$G$79,$O15)="","",INDEX(전체!$G$10:$G$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="G15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$H$10:$H$79,$O15)="","",INDEX(전체!$H$10:$H$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="H15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$I$10:$I$79,$O15)="","",INDEX(전체!$I$10:$I$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="I15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$J$10:$J$79,$O15)="","",INDEX(전체!$J$10:$J$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$K$10:$K$79,$O15)="","",INDEX(전체!$K$10:$K$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="K15" s="18" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$Q$10:$Q$79,$O15)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O15),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$M$10:$M$79,$O15)="","",INDEX(전체!$M$10:$M$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="M15" s="11" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$N$10:$N$79,$O15)="","",INDEX(전체!$N$10:$N$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="N15" s="29" t="str">
+        <f aca="false">IF($O15="","",IF(INDEX(전체!$O$10:$O$79,$O15)="","",INDEX(전체!$O$10:$O$79,$O15)))</f>
+        <v/>
+      </c>
+      <c r="O15" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;11,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="str">
+        <f aca="false">IF($O16="","",12)</f>
+        <v/>
+      </c>
+      <c r="B16" s="28" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$C$10:$C$79,$O16)="","",INDEX(전체!$C$10:$C$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="C16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$D$10:$D$79,$O16)="","",INDEX(전체!$D$10:$D$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="D16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$E$10:$E$79,$O16)="","",INDEX(전체!$E$10:$E$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="E16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$F$10:$F$79,$O16)="","",INDEX(전체!$F$10:$F$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="F16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$G$10:$G$79,$O16)="","",INDEX(전체!$G$10:$G$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="G16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$H$10:$H$79,$O16)="","",INDEX(전체!$H$10:$H$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="H16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$I$10:$I$79,$O16)="","",INDEX(전체!$I$10:$I$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="I16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$J$10:$J$79,$O16)="","",INDEX(전체!$J$10:$J$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$K$10:$K$79,$O16)="","",INDEX(전체!$K$10:$K$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="K16" s="18" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$Q$10:$Q$79,$O16)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O16),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$M$10:$M$79,$O16)="","",INDEX(전체!$M$10:$M$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="M16" s="11" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$N$10:$N$79,$O16)="","",INDEX(전체!$N$10:$N$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="N16" s="29" t="str">
+        <f aca="false">IF($O16="","",IF(INDEX(전체!$O$10:$O$79,$O16)="","",INDEX(전체!$O$10:$O$79,$O16)))</f>
+        <v/>
+      </c>
+      <c r="O16" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;12,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="str">
+        <f aca="false">IF($O17="","",13)</f>
+        <v/>
+      </c>
+      <c r="B17" s="28" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$C$10:$C$79,$O17)="","",INDEX(전체!$C$10:$C$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="C17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$D$10:$D$79,$O17)="","",INDEX(전체!$D$10:$D$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="D17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$E$10:$E$79,$O17)="","",INDEX(전체!$E$10:$E$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="E17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$F$10:$F$79,$O17)="","",INDEX(전체!$F$10:$F$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="F17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$G$10:$G$79,$O17)="","",INDEX(전체!$G$10:$G$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="G17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$H$10:$H$79,$O17)="","",INDEX(전체!$H$10:$H$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="H17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$I$10:$I$79,$O17)="","",INDEX(전체!$I$10:$I$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="I17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$J$10:$J$79,$O17)="","",INDEX(전체!$J$10:$J$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$K$10:$K$79,$O17)="","",INDEX(전체!$K$10:$K$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="18" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$Q$10:$Q$79,$O17)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O17),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$M$10:$M$79,$O17)="","",INDEX(전체!$M$10:$M$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="M17" s="11" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$N$10:$N$79,$O17)="","",INDEX(전체!$N$10:$N$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="N17" s="29" t="str">
+        <f aca="false">IF($O17="","",IF(INDEX(전체!$O$10:$O$79,$O17)="","",INDEX(전체!$O$10:$O$79,$O17)))</f>
+        <v/>
+      </c>
+      <c r="O17" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;13,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="str">
+        <f aca="false">IF($O18="","",14)</f>
+        <v/>
+      </c>
+      <c r="B18" s="28" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$C$10:$C$79,$O18)="","",INDEX(전체!$C$10:$C$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="C18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$D$10:$D$79,$O18)="","",INDEX(전체!$D$10:$D$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="D18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$E$10:$E$79,$O18)="","",INDEX(전체!$E$10:$E$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="E18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$F$10:$F$79,$O18)="","",INDEX(전체!$F$10:$F$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="F18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$G$10:$G$79,$O18)="","",INDEX(전체!$G$10:$G$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="G18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$H$10:$H$79,$O18)="","",INDEX(전체!$H$10:$H$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="H18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$I$10:$I$79,$O18)="","",INDEX(전체!$I$10:$I$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="I18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$J$10:$J$79,$O18)="","",INDEX(전체!$J$10:$J$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$K$10:$K$79,$O18)="","",INDEX(전체!$K$10:$K$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="K18" s="18" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$Q$10:$Q$79,$O18)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O18),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$M$10:$M$79,$O18)="","",INDEX(전체!$M$10:$M$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="M18" s="11" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$N$10:$N$79,$O18)="","",INDEX(전체!$N$10:$N$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="N18" s="29" t="str">
+        <f aca="false">IF($O18="","",IF(INDEX(전체!$O$10:$O$79,$O18)="","",INDEX(전체!$O$10:$O$79,$O18)))</f>
+        <v/>
+      </c>
+      <c r="O18" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;14,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="str">
+        <f aca="false">IF($O19="","",15)</f>
+        <v/>
+      </c>
+      <c r="B19" s="28" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$C$10:$C$79,$O19)="","",INDEX(전체!$C$10:$C$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="C19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$D$10:$D$79,$O19)="","",INDEX(전체!$D$10:$D$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="D19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$E$10:$E$79,$O19)="","",INDEX(전체!$E$10:$E$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="E19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$F$10:$F$79,$O19)="","",INDEX(전체!$F$10:$F$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$G$10:$G$79,$O19)="","",INDEX(전체!$G$10:$G$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="G19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$H$10:$H$79,$O19)="","",INDEX(전체!$H$10:$H$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="H19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$I$10:$I$79,$O19)="","",INDEX(전체!$I$10:$I$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="I19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$J$10:$J$79,$O19)="","",INDEX(전체!$J$10:$J$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$K$10:$K$79,$O19)="","",INDEX(전체!$K$10:$K$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="K19" s="18" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$Q$10:$Q$79,$O19)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O19),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$M$10:$M$79,$O19)="","",INDEX(전체!$M$10:$M$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="M19" s="11" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$N$10:$N$79,$O19)="","",INDEX(전체!$N$10:$N$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="29" t="str">
+        <f aca="false">IF($O19="","",IF(INDEX(전체!$O$10:$O$79,$O19)="","",INDEX(전체!$O$10:$O$79,$O19)))</f>
+        <v/>
+      </c>
+      <c r="O19" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;15,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="str">
+        <f aca="false">IF($O20="","",16)</f>
+        <v/>
+      </c>
+      <c r="B20" s="28" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$C$10:$C$79,$O20)="","",INDEX(전체!$C$10:$C$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="C20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$D$10:$D$79,$O20)="","",INDEX(전체!$D$10:$D$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="D20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$E$10:$E$79,$O20)="","",INDEX(전체!$E$10:$E$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="E20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$F$10:$F$79,$O20)="","",INDEX(전체!$F$10:$F$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="F20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$G$10:$G$79,$O20)="","",INDEX(전체!$G$10:$G$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="G20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$H$10:$H$79,$O20)="","",INDEX(전체!$H$10:$H$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="H20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$I$10:$I$79,$O20)="","",INDEX(전체!$I$10:$I$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="I20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$J$10:$J$79,$O20)="","",INDEX(전체!$J$10:$J$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$K$10:$K$79,$O20)="","",INDEX(전체!$K$10:$K$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="18" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$Q$10:$Q$79,$O20)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O20),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$M$10:$M$79,$O20)="","",INDEX(전체!$M$10:$M$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="M20" s="11" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$N$10:$N$79,$O20)="","",INDEX(전체!$N$10:$N$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="N20" s="29" t="str">
+        <f aca="false">IF($O20="","",IF(INDEX(전체!$O$10:$O$79,$O20)="","",INDEX(전체!$O$10:$O$79,$O20)))</f>
+        <v/>
+      </c>
+      <c r="O20" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;16,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="str">
+        <f aca="false">IF($O21="","",17)</f>
+        <v/>
+      </c>
+      <c r="B21" s="28" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$C$10:$C$79,$O21)="","",INDEX(전체!$C$10:$C$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="C21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$D$10:$D$79,$O21)="","",INDEX(전체!$D$10:$D$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="D21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$E$10:$E$79,$O21)="","",INDEX(전체!$E$10:$E$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="E21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$F$10:$F$79,$O21)="","",INDEX(전체!$F$10:$F$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="F21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$G$10:$G$79,$O21)="","",INDEX(전체!$G$10:$G$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$H$10:$H$79,$O21)="","",INDEX(전체!$H$10:$H$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="H21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$I$10:$I$79,$O21)="","",INDEX(전체!$I$10:$I$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="I21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$J$10:$J$79,$O21)="","",INDEX(전체!$J$10:$J$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$K$10:$K$79,$O21)="","",INDEX(전체!$K$10:$K$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="K21" s="18" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$Q$10:$Q$79,$O21)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O21),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$M$10:$M$79,$O21)="","",INDEX(전체!$M$10:$M$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="M21" s="11" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$N$10:$N$79,$O21)="","",INDEX(전체!$N$10:$N$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="N21" s="29" t="str">
+        <f aca="false">IF($O21="","",IF(INDEX(전체!$O$10:$O$79,$O21)="","",INDEX(전체!$O$10:$O$79,$O21)))</f>
+        <v/>
+      </c>
+      <c r="O21" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;17,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="str">
+        <f aca="false">IF($O22="","",18)</f>
+        <v/>
+      </c>
+      <c r="B22" s="28" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$C$10:$C$79,$O22)="","",INDEX(전체!$C$10:$C$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="C22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$D$10:$D$79,$O22)="","",INDEX(전체!$D$10:$D$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="D22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$E$10:$E$79,$O22)="","",INDEX(전체!$E$10:$E$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="E22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$F$10:$F$79,$O22)="","",INDEX(전체!$F$10:$F$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$G$10:$G$79,$O22)="","",INDEX(전체!$G$10:$G$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$H$10:$H$79,$O22)="","",INDEX(전체!$H$10:$H$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$I$10:$I$79,$O22)="","",INDEX(전체!$I$10:$I$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$J$10:$J$79,$O22)="","",INDEX(전체!$J$10:$J$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$K$10:$K$79,$O22)="","",INDEX(전체!$K$10:$K$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="K22" s="18" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$Q$10:$Q$79,$O22)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O22),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$M$10:$M$79,$O22)="","",INDEX(전체!$M$10:$M$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="11" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$N$10:$N$79,$O22)="","",INDEX(전체!$N$10:$N$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="N22" s="29" t="str">
+        <f aca="false">IF($O22="","",IF(INDEX(전체!$O$10:$O$79,$O22)="","",INDEX(전체!$O$10:$O$79,$O22)))</f>
+        <v/>
+      </c>
+      <c r="O22" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;18,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="str">
+        <f aca="false">IF($O23="","",19)</f>
+        <v/>
+      </c>
+      <c r="B23" s="28" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$C$10:$C$79,$O23)="","",INDEX(전체!$C$10:$C$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="C23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$D$10:$D$79,$O23)="","",INDEX(전체!$D$10:$D$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="D23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$E$10:$E$79,$O23)="","",INDEX(전체!$E$10:$E$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="E23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$F$10:$F$79,$O23)="","",INDEX(전체!$F$10:$F$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="F23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$G$10:$G$79,$O23)="","",INDEX(전체!$G$10:$G$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$H$10:$H$79,$O23)="","",INDEX(전체!$H$10:$H$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="H23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$I$10:$I$79,$O23)="","",INDEX(전체!$I$10:$I$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$J$10:$J$79,$O23)="","",INDEX(전체!$J$10:$J$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$K$10:$K$79,$O23)="","",INDEX(전체!$K$10:$K$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="K23" s="18" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$Q$10:$Q$79,$O23)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O23),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$M$10:$M$79,$O23)="","",INDEX(전체!$M$10:$M$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="M23" s="11" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$N$10:$N$79,$O23)="","",INDEX(전체!$N$10:$N$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="N23" s="29" t="str">
+        <f aca="false">IF($O23="","",IF(INDEX(전체!$O$10:$O$79,$O23)="","",INDEX(전체!$O$10:$O$79,$O23)))</f>
+        <v/>
+      </c>
+      <c r="O23" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;19,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="str">
+        <f aca="false">IF($O24="","",20)</f>
+        <v/>
+      </c>
+      <c r="B24" s="28" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$C$10:$C$79,$O24)="","",INDEX(전체!$C$10:$C$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="C24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$D$10:$D$79,$O24)="","",INDEX(전체!$D$10:$D$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="D24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$E$10:$E$79,$O24)="","",INDEX(전체!$E$10:$E$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="E24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$F$10:$F$79,$O24)="","",INDEX(전체!$F$10:$F$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="F24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$G$10:$G$79,$O24)="","",INDEX(전체!$G$10:$G$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$H$10:$H$79,$O24)="","",INDEX(전체!$H$10:$H$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$I$10:$I$79,$O24)="","",INDEX(전체!$I$10:$I$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="I24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$J$10:$J$79,$O24)="","",INDEX(전체!$J$10:$J$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$K$10:$K$79,$O24)="","",INDEX(전체!$K$10:$K$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="K24" s="18" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$Q$10:$Q$79,$O24)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O24),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$M$10:$M$79,$O24)="","",INDEX(전체!$M$10:$M$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="M24" s="11" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$N$10:$N$79,$O24)="","",INDEX(전체!$N$10:$N$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="N24" s="29" t="str">
+        <f aca="false">IF($O24="","",IF(INDEX(전체!$O$10:$O$79,$O24)="","",INDEX(전체!$O$10:$O$79,$O24)))</f>
+        <v/>
+      </c>
+      <c r="O24" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;20,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="str">
+        <f aca="false">IF($O25="","",21)</f>
+        <v/>
+      </c>
+      <c r="B25" s="28" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$C$10:$C$79,$O25)="","",INDEX(전체!$C$10:$C$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="C25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$D$10:$D$79,$O25)="","",INDEX(전체!$D$10:$D$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="D25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$E$10:$E$79,$O25)="","",INDEX(전체!$E$10:$E$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="E25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$F$10:$F$79,$O25)="","",INDEX(전체!$F$10:$F$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="F25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$G$10:$G$79,$O25)="","",INDEX(전체!$G$10:$G$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$H$10:$H$79,$O25)="","",INDEX(전체!$H$10:$H$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$I$10:$I$79,$O25)="","",INDEX(전체!$I$10:$I$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$J$10:$J$79,$O25)="","",INDEX(전체!$J$10:$J$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$K$10:$K$79,$O25)="","",INDEX(전체!$K$10:$K$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="K25" s="18" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$Q$10:$Q$79,$O25)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O25),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$M$10:$M$79,$O25)="","",INDEX(전체!$M$10:$M$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="M25" s="11" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$N$10:$N$79,$O25)="","",INDEX(전체!$N$10:$N$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="N25" s="29" t="str">
+        <f aca="false">IF($O25="","",IF(INDEX(전체!$O$10:$O$79,$O25)="","",INDEX(전체!$O$10:$O$79,$O25)))</f>
+        <v/>
+      </c>
+      <c r="O25" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;21,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="str">
+        <f aca="false">IF($O26="","",22)</f>
+        <v/>
+      </c>
+      <c r="B26" s="28" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$C$10:$C$79,$O26)="","",INDEX(전체!$C$10:$C$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="C26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$D$10:$D$79,$O26)="","",INDEX(전체!$D$10:$D$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="D26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$E$10:$E$79,$O26)="","",INDEX(전체!$E$10:$E$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$F$10:$F$79,$O26)="","",INDEX(전체!$F$10:$F$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$G$10:$G$79,$O26)="","",INDEX(전체!$G$10:$G$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$H$10:$H$79,$O26)="","",INDEX(전체!$H$10:$H$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$I$10:$I$79,$O26)="","",INDEX(전체!$I$10:$I$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$J$10:$J$79,$O26)="","",INDEX(전체!$J$10:$J$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$K$10:$K$79,$O26)="","",INDEX(전체!$K$10:$K$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="K26" s="18" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$Q$10:$Q$79,$O26)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O26),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$M$10:$M$79,$O26)="","",INDEX(전체!$M$10:$M$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="M26" s="11" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$N$10:$N$79,$O26)="","",INDEX(전체!$N$10:$N$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="29" t="str">
+        <f aca="false">IF($O26="","",IF(INDEX(전체!$O$10:$O$79,$O26)="","",INDEX(전체!$O$10:$O$79,$O26)))</f>
+        <v/>
+      </c>
+      <c r="O26" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;22,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="str">
+        <f aca="false">IF($O27="","",23)</f>
+        <v/>
+      </c>
+      <c r="B27" s="28" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$C$10:$C$79,$O27)="","",INDEX(전체!$C$10:$C$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="C27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$D$10:$D$79,$O27)="","",INDEX(전체!$D$10:$D$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="D27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$E$10:$E$79,$O27)="","",INDEX(전체!$E$10:$E$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="E27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$F$10:$F$79,$O27)="","",INDEX(전체!$F$10:$F$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="F27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$G$10:$G$79,$O27)="","",INDEX(전체!$G$10:$G$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$H$10:$H$79,$O27)="","",INDEX(전체!$H$10:$H$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$I$10:$I$79,$O27)="","",INDEX(전체!$I$10:$I$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="I27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$J$10:$J$79,$O27)="","",INDEX(전체!$J$10:$J$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$K$10:$K$79,$O27)="","",INDEX(전체!$K$10:$K$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="K27" s="18" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$Q$10:$Q$79,$O27)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O27),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$M$10:$M$79,$O27)="","",INDEX(전체!$M$10:$M$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="M27" s="11" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$N$10:$N$79,$O27)="","",INDEX(전체!$N$10:$N$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="N27" s="29" t="str">
+        <f aca="false">IF($O27="","",IF(INDEX(전체!$O$10:$O$79,$O27)="","",INDEX(전체!$O$10:$O$79,$O27)))</f>
+        <v/>
+      </c>
+      <c r="O27" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;23,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="str">
+        <f aca="false">IF($O28="","",24)</f>
+        <v/>
+      </c>
+      <c r="B28" s="28" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$C$10:$C$79,$O28)="","",INDEX(전체!$C$10:$C$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="C28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$D$10:$D$79,$O28)="","",INDEX(전체!$D$10:$D$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="D28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$E$10:$E$79,$O28)="","",INDEX(전체!$E$10:$E$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="E28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$F$10:$F$79,$O28)="","",INDEX(전체!$F$10:$F$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$G$10:$G$79,$O28)="","",INDEX(전체!$G$10:$G$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$H$10:$H$79,$O28)="","",INDEX(전체!$H$10:$H$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$I$10:$I$79,$O28)="","",INDEX(전체!$I$10:$I$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$J$10:$J$79,$O28)="","",INDEX(전체!$J$10:$J$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$K$10:$K$79,$O28)="","",INDEX(전체!$K$10:$K$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="K28" s="18" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$Q$10:$Q$79,$O28)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O28),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$M$10:$M$79,$O28)="","",INDEX(전체!$M$10:$M$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="M28" s="11" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$N$10:$N$79,$O28)="","",INDEX(전체!$N$10:$N$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="N28" s="29" t="str">
+        <f aca="false">IF($O28="","",IF(INDEX(전체!$O$10:$O$79,$O28)="","",INDEX(전체!$O$10:$O$79,$O28)))</f>
+        <v/>
+      </c>
+      <c r="O28" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;24,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="str">
+        <f aca="false">IF($O29="","",25)</f>
+        <v/>
+      </c>
+      <c r="B29" s="28" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$C$10:$C$79,$O29)="","",INDEX(전체!$C$10:$C$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="C29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$D$10:$D$79,$O29)="","",INDEX(전체!$D$10:$D$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="D29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$E$10:$E$79,$O29)="","",INDEX(전체!$E$10:$E$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="E29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$F$10:$F$79,$O29)="","",INDEX(전체!$F$10:$F$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="F29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$G$10:$G$79,$O29)="","",INDEX(전체!$G$10:$G$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="G29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$H$10:$H$79,$O29)="","",INDEX(전체!$H$10:$H$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$I$10:$I$79,$O29)="","",INDEX(전체!$I$10:$I$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="I29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$J$10:$J$79,$O29)="","",INDEX(전체!$J$10:$J$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$K$10:$K$79,$O29)="","",INDEX(전체!$K$10:$K$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="K29" s="18" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$Q$10:$Q$79,$O29)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O29),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$M$10:$M$79,$O29)="","",INDEX(전체!$M$10:$M$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="M29" s="11" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$N$10:$N$79,$O29)="","",INDEX(전체!$N$10:$N$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="N29" s="29" t="str">
+        <f aca="false">IF($O29="","",IF(INDEX(전체!$O$10:$O$79,$O29)="","",INDEX(전체!$O$10:$O$79,$O29)))</f>
+        <v/>
+      </c>
+      <c r="O29" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;25,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFD9D9D9"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="24" t="str">
+        <f aca="false">COUNTIF(전체!$B$10:$B$79,"기타")&amp;"곳"</f>
+        <v>1곳</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q2" s="26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="n">
+        <f aca="false">IF($O5="","",1)</f>
+        <v>1</v>
+      </c>
+      <c r="B5" s="28" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$C$10:$C$79,$O5)="","",INDEX(전체!$C$10:$C$79,$O5)))</f>
+        <v>미쓰부산</v>
+      </c>
+      <c r="C5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$D$10:$D$79,$O5)="","",INDEX(전체!$D$10:$D$79,$O5)))</f>
+        <v>확인 필요</v>
+      </c>
+      <c r="D5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$E$10:$E$79,$O5)="","",INDEX(전체!$E$10:$E$79,$O5)))</f>
+        <v>정보 없음</v>
+      </c>
+      <c r="E5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$F$10:$F$79,$O5)="","",INDEX(전체!$F$10:$F$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="F5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$G$10:$G$79,$O5)="","",INDEX(전체!$G$10:$G$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="G5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$H$10:$H$79,$O5)="","",INDEX(전체!$H$10:$H$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="H5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$I$10:$I$79,$O5)="","",INDEX(전체!$I$10:$I$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="I5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$J$10:$J$79,$O5)="","",INDEX(전체!$J$10:$J$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="J5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$K$10:$K$79,$O5)="","",INDEX(전체!$K$10:$K$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="K5" s="18" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$Q$10:$Q$79,$O5)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O5),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$M$10:$M$79,$O5)="","",INDEX(전체!$M$10:$M$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="M5" s="11" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$N$10:$N$79,$O5)="","",INDEX(전체!$N$10:$N$79,$O5)))</f>
+        <v/>
+      </c>
+      <c r="N5" s="29" t="str">
+        <f aca="false">IF($O5="","",IF(INDEX(전체!$O$10:$O$79,$O5)="","",INDEX(전체!$O$10:$O$79,$O5)))</f>
+        <v>이름만 받음 – 업종·위치 확인 필요</v>
+      </c>
+      <c r="O5" s="30" t="n">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;1,전체!$P$10:$P$79,0),"")</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="str">
+        <f aca="false">IF($O6="","",2)</f>
+        <v/>
+      </c>
+      <c r="B6" s="28" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$C$10:$C$79,$O6)="","",INDEX(전체!$C$10:$C$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="C6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$D$10:$D$79,$O6)="","",INDEX(전체!$D$10:$D$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="D6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$E$10:$E$79,$O6)="","",INDEX(전체!$E$10:$E$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="E6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$F$10:$F$79,$O6)="","",INDEX(전체!$F$10:$F$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="F6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$G$10:$G$79,$O6)="","",INDEX(전체!$G$10:$G$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="G6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$H$10:$H$79,$O6)="","",INDEX(전체!$H$10:$H$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="H6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$I$10:$I$79,$O6)="","",INDEX(전체!$I$10:$I$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="I6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$J$10:$J$79,$O6)="","",INDEX(전체!$J$10:$J$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="J6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$K$10:$K$79,$O6)="","",INDEX(전체!$K$10:$K$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="K6" s="18" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$Q$10:$Q$79,$O6)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O6),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$M$10:$M$79,$O6)="","",INDEX(전체!$M$10:$M$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="11" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$N$10:$N$79,$O6)="","",INDEX(전체!$N$10:$N$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="N6" s="29" t="str">
+        <f aca="false">IF($O6="","",IF(INDEX(전체!$O$10:$O$79,$O6)="","",INDEX(전체!$O$10:$O$79,$O6)))</f>
+        <v/>
+      </c>
+      <c r="O6" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;2,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="str">
+        <f aca="false">IF($O7="","",3)</f>
+        <v/>
+      </c>
+      <c r="B7" s="28" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$C$10:$C$79,$O7)="","",INDEX(전체!$C$10:$C$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="C7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$D$10:$D$79,$O7)="","",INDEX(전체!$D$10:$D$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="D7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$E$10:$E$79,$O7)="","",INDEX(전체!$E$10:$E$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="E7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$F$10:$F$79,$O7)="","",INDEX(전체!$F$10:$F$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$G$10:$G$79,$O7)="","",INDEX(전체!$G$10:$G$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="G7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$H$10:$H$79,$O7)="","",INDEX(전체!$H$10:$H$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="H7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$I$10:$I$79,$O7)="","",INDEX(전체!$I$10:$I$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$J$10:$J$79,$O7)="","",INDEX(전체!$J$10:$J$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$K$10:$K$79,$O7)="","",INDEX(전체!$K$10:$K$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="K7" s="18" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$Q$10:$Q$79,$O7)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O7),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$M$10:$M$79,$O7)="","",INDEX(전체!$M$10:$M$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="11" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$N$10:$N$79,$O7)="","",INDEX(전체!$N$10:$N$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="N7" s="29" t="str">
+        <f aca="false">IF($O7="","",IF(INDEX(전체!$O$10:$O$79,$O7)="","",INDEX(전체!$O$10:$O$79,$O7)))</f>
+        <v/>
+      </c>
+      <c r="O7" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;3,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="str">
+        <f aca="false">IF($O8="","",4)</f>
+        <v/>
+      </c>
+      <c r="B8" s="28" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$C$10:$C$79,$O8)="","",INDEX(전체!$C$10:$C$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="C8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$D$10:$D$79,$O8)="","",INDEX(전체!$D$10:$D$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="D8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$E$10:$E$79,$O8)="","",INDEX(전체!$E$10:$E$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="E8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$F$10:$F$79,$O8)="","",INDEX(전체!$F$10:$F$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="F8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$G$10:$G$79,$O8)="","",INDEX(전체!$G$10:$G$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$H$10:$H$79,$O8)="","",INDEX(전체!$H$10:$H$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="H8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$I$10:$I$79,$O8)="","",INDEX(전체!$I$10:$I$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$J$10:$J$79,$O8)="","",INDEX(전체!$J$10:$J$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$K$10:$K$79,$O8)="","",INDEX(전체!$K$10:$K$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="K8" s="18" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$Q$10:$Q$79,$O8)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O8),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$M$10:$M$79,$O8)="","",INDEX(전체!$M$10:$M$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="11" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$N$10:$N$79,$O8)="","",INDEX(전체!$N$10:$N$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="N8" s="29" t="str">
+        <f aca="false">IF($O8="","",IF(INDEX(전체!$O$10:$O$79,$O8)="","",INDEX(전체!$O$10:$O$79,$O8)))</f>
+        <v/>
+      </c>
+      <c r="O8" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;4,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="str">
+        <f aca="false">IF($O9="","",5)</f>
+        <v/>
+      </c>
+      <c r="B9" s="28" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$C$10:$C$79,$O9)="","",INDEX(전체!$C$10:$C$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="C9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$D$10:$D$79,$O9)="","",INDEX(전체!$D$10:$D$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="D9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$E$10:$E$79,$O9)="","",INDEX(전체!$E$10:$E$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="E9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$F$10:$F$79,$O9)="","",INDEX(전체!$F$10:$F$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="F9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$G$10:$G$79,$O9)="","",INDEX(전체!$G$10:$G$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="G9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$H$10:$H$79,$O9)="","",INDEX(전체!$H$10:$H$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="H9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$I$10:$I$79,$O9)="","",INDEX(전체!$I$10:$I$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$J$10:$J$79,$O9)="","",INDEX(전체!$J$10:$J$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$K$10:$K$79,$O9)="","",INDEX(전체!$K$10:$K$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="18" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$Q$10:$Q$79,$O9)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O9),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$M$10:$M$79,$O9)="","",INDEX(전체!$M$10:$M$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="11" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$N$10:$N$79,$O9)="","",INDEX(전체!$N$10:$N$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="N9" s="29" t="str">
+        <f aca="false">IF($O9="","",IF(INDEX(전체!$O$10:$O$79,$O9)="","",INDEX(전체!$O$10:$O$79,$O9)))</f>
+        <v/>
+      </c>
+      <c r="O9" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;5,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="str">
+        <f aca="false">IF($O10="","",6)</f>
+        <v/>
+      </c>
+      <c r="B10" s="28" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$C$10:$C$79,$O10)="","",INDEX(전체!$C$10:$C$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="C10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$D$10:$D$79,$O10)="","",INDEX(전체!$D$10:$D$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="D10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$E$10:$E$79,$O10)="","",INDEX(전체!$E$10:$E$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="E10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$F$10:$F$79,$O10)="","",INDEX(전체!$F$10:$F$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="F10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$G$10:$G$79,$O10)="","",INDEX(전체!$G$10:$G$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="G10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$H$10:$H$79,$O10)="","",INDEX(전체!$H$10:$H$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$I$10:$I$79,$O10)="","",INDEX(전체!$I$10:$I$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$J$10:$J$79,$O10)="","",INDEX(전체!$J$10:$J$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$K$10:$K$79,$O10)="","",INDEX(전체!$K$10:$K$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="18" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$Q$10:$Q$79,$O10)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O10),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$M$10:$M$79,$O10)="","",INDEX(전체!$M$10:$M$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="11" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$N$10:$N$79,$O10)="","",INDEX(전체!$N$10:$N$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="N10" s="29" t="str">
+        <f aca="false">IF($O10="","",IF(INDEX(전체!$O$10:$O$79,$O10)="","",INDEX(전체!$O$10:$O$79,$O10)))</f>
+        <v/>
+      </c>
+      <c r="O10" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;6,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="str">
+        <f aca="false">IF($O11="","",7)</f>
+        <v/>
+      </c>
+      <c r="B11" s="28" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$C$10:$C$79,$O11)="","",INDEX(전체!$C$10:$C$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="C11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$D$10:$D$79,$O11)="","",INDEX(전체!$D$10:$D$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="D11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$E$10:$E$79,$O11)="","",INDEX(전체!$E$10:$E$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="E11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$F$10:$F$79,$O11)="","",INDEX(전체!$F$10:$F$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="F11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$G$10:$G$79,$O11)="","",INDEX(전체!$G$10:$G$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="G11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$H$10:$H$79,$O11)="","",INDEX(전체!$H$10:$H$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="H11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$I$10:$I$79,$O11)="","",INDEX(전체!$I$10:$I$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$J$10:$J$79,$O11)="","",INDEX(전체!$J$10:$J$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$K$10:$K$79,$O11)="","",INDEX(전체!$K$10:$K$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="18" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$Q$10:$Q$79,$O11)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O11),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$M$10:$M$79,$O11)="","",INDEX(전체!$M$10:$M$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="11" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$N$10:$N$79,$O11)="","",INDEX(전체!$N$10:$N$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="N11" s="29" t="str">
+        <f aca="false">IF($O11="","",IF(INDEX(전체!$O$10:$O$79,$O11)="","",INDEX(전체!$O$10:$O$79,$O11)))</f>
+        <v/>
+      </c>
+      <c r="O11" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;7,전체!$P$10:$P$79,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="str">
+        <f aca="false">IF($O12="","",8)</f>
+        <v/>
+      </c>
+      <c r="B12" s="28" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$C$10:$C$79,$O12)="","",INDEX(전체!$C$10:$C$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="C12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$D$10:$D$79,$O12)="","",INDEX(전체!$D$10:$D$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="D12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$E$10:$E$79,$O12)="","",INDEX(전체!$E$10:$E$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="E12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$F$10:$F$79,$O12)="","",INDEX(전체!$F$10:$F$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="F12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$G$10:$G$79,$O12)="","",INDEX(전체!$G$10:$G$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="G12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$H$10:$H$79,$O12)="","",INDEX(전체!$H$10:$H$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="H12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$I$10:$I$79,$O12)="","",INDEX(전체!$I$10:$I$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$J$10:$J$79,$O12)="","",INDEX(전체!$J$10:$J$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$K$10:$K$79,$O12)="","",INDEX(전체!$K$10:$K$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="18" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$Q$10:$Q$79,$O12)="","",HYPERLINK(INDEX(전체!$Q$10:$Q$79,$O12),"지도")))</f>
+        <v/>
+      </c>
+      <c r="L12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$M$10:$M$79,$O12)="","",INDEX(전체!$M$10:$M$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="11" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$N$10:$N$79,$O12)="","",INDEX(전체!$N$10:$N$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="29" t="str">
+        <f aca="false">IF($O12="","",IF(INDEX(전체!$O$10:$O$79,$O12)="","",INDEX(전체!$O$10:$O$79,$O12)))</f>
+        <v/>
+      </c>
+      <c r="O12" s="30" t="str">
+        <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;8,전체!$P$10:$P$79,0),"")</f>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8777,7 +12994,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
         <v>44</v>
@@ -8821,13 +13038,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10418,7 +14635,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="C1" s="24" t="str">
         <f aca="false">COUNTIF(전체!$B$10:$B$79,"고기·족발")&amp;"곳"</f>
@@ -10427,10 +14644,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10471,13 +14688,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12068,7 +16285,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="C1" s="24" t="str">
         <f aca="false">COUNTIF(전체!$B$10:$B$79,"국밥·탕")&amp;"곳"</f>
@@ -12077,10 +16294,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12121,13 +16338,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13727,7 +17944,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
         <v>52</v>
@@ -13771,13 +17988,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15377,7 +19594,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
         <v>28</v>
@@ -15421,13 +19638,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17022,12 +21239,12 @@
       </c>
       <c r="C1" s="24" t="str">
         <f aca="false">COUNTIF(전체!$B$10:$B$79,"일식")&amp;"곳"</f>
-        <v>3곳</v>
+        <v>4곳</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
         <v>34</v>
@@ -17071,13 +21288,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17266,22 +21483,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="str">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
         <f aca="false">IF($O8="","",4)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="B8" s="28" t="str">
         <f aca="false">IF($O8="","",IF(INDEX(전체!$C$10:$C$79,$O8)="","",INDEX(전체!$C$10:$C$79,$O8)))</f>
-        <v/>
+        <v>샤브남바완</v>
       </c>
       <c r="C8" s="29" t="str">
         <f aca="false">IF($O8="","",IF(INDEX(전체!$D$10:$D$79,$O8)="","",INDEX(전체!$D$10:$D$79,$O8)))</f>
-        <v/>
+        <v>샤브샤브 (추정)</v>
       </c>
       <c r="D8" s="11" t="str">
         <f aca="false">IF($O8="","",IF(INDEX(전체!$E$10:$E$79,$O8)="","",INDEX(전체!$E$10:$E$79,$O8)))</f>
-        <v/>
+        <v>정보 없음</v>
       </c>
       <c r="E8" s="11" t="str">
         <f aca="false">IF($O8="","",IF(INDEX(전체!$F$10:$F$79,$O8)="","",INDEX(전체!$F$10:$F$79,$O8)))</f>
@@ -17321,11 +21538,11 @@
       </c>
       <c r="N8" s="29" t="str">
         <f aca="false">IF($O8="","",IF(INDEX(전체!$O$10:$O$79,$O8)="","",INDEX(전체!$O$10:$O$79,$O8)))</f>
-        <v/>
-      </c>
-      <c r="O8" s="30" t="str">
+        <v>이름만 받음 – 위치·업종 확인 필요 (분류 추정)</v>
+      </c>
+      <c r="O8" s="30" t="n">
         <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;4,전체!$P$10:$P$79,0),"")</f>
-        <v/>
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18668,7 +22885,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="C1" s="24" t="str">
         <f aca="false">COUNTIF(전체!$B$10:$B$79,"회·해산물")&amp;"곳"</f>
@@ -18677,10 +22894,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18721,13 +22938,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20318,19 +24535,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="C1" s="24" t="str">
         <f aca="false">COUNTIF(전체!$B$10:$B$79,"양식·아시안")&amp;"곳"</f>
-        <v>1곳</v>
+        <v>2곳</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="26" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20371,13 +24588,13 @@
         <v>23</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20443,21 +24660,21 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="str">
+      <c r="A6" s="11" t="n">
         <f aca="false">IF($O6="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="B6" s="28" t="str">
         <f aca="false">IF($O6="","",IF(INDEX(전체!$C$10:$C$79,$O6)="","",INDEX(전체!$C$10:$C$79,$O6)))</f>
-        <v/>
+        <v>이재모피자 (광복동)</v>
       </c>
       <c r="C6" s="29" t="str">
         <f aca="false">IF($O6="","",IF(INDEX(전체!$D$10:$D$79,$O6)="","",INDEX(전체!$D$10:$D$79,$O6)))</f>
-        <v/>
+        <v>피자 (추정)</v>
       </c>
       <c r="D6" s="11" t="str">
         <f aca="false">IF($O6="","",IF(INDEX(전체!$E$10:$E$79,$O6)="","",INDEX(전체!$E$10:$E$79,$O6)))</f>
-        <v/>
+        <v>정보 없음</v>
       </c>
       <c r="E6" s="11" t="str">
         <f aca="false">IF($O6="","",IF(INDEX(전체!$F$10:$F$79,$O6)="","",INDEX(전체!$F$10:$F$79,$O6)))</f>
@@ -20465,7 +24682,7 @@
       </c>
       <c r="F6" s="29" t="str">
         <f aca="false">IF($O6="","",IF(INDEX(전체!$G$10:$G$79,$O6)="","",INDEX(전체!$G$10:$G$79,$O6)))</f>
-        <v/>
+        <v>광복동 (상세 주소 확인 필요)</v>
       </c>
       <c r="G6" s="29" t="str">
         <f aca="false">IF($O6="","",IF(INDEX(전체!$H$10:$H$79,$O6)="","",INDEX(전체!$H$10:$H$79,$O6)))</f>
@@ -20497,11 +24714,11 @@
       </c>
       <c r="N6" s="29" t="str">
         <f aca="false">IF($O6="","",IF(INDEX(전체!$O$10:$O$79,$O6)="","",INDEX(전체!$O$10:$O$79,$O6)))</f>
-        <v/>
-      </c>
-      <c r="O6" s="30" t="str">
+        <v>업종·상세는 이름만 받음 – 확인 필요</v>
+      </c>
+      <c r="O6" s="30" t="n">
         <f aca="false">IFERROR(MATCH($Q$2&amp;"|"&amp;2,전체!$P$10:$P$79,0),"")</f>
-        <v/>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
